--- a/weekly-deals/outputs/Weekly_Fintech_Deals_2026-06-26.xlsx
+++ b/weekly-deals/outputs/Weekly_Fintech_Deals_2026-06-26.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="M&amp;A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All M&amp;A (PE &amp; Strategic)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Growth Capital Raises" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M&amp;A'!$A$1:$L$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$A$1:$R$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,453 +460,478 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="54" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Target Country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Deal Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acquirer</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EV ($M)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EV / Revenue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Target Description</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Link / Press Release</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Financials &amp; basis (notes)</t>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Mults Source</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mults Basis</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Public Deal</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>HL Deal</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Seller</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Asset &amp; Wealth Tech</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>22-Jun-26</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Marstone</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>FusionIQ</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>Digital wealth-management platform (digital advice, financial planning and wellness) for banks, credit unions, and wealth managers</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Terms undisclosed (completed acquisition). Combines with FusionIQ's cloud-based wealth-management platform.</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Banking &amp; Lending Tech</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>23-Jun-26</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Kasisto</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Backbase</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Pioneer of agentic/conversational AI for banking, partnered with ~55 financial institutions across 16 countries</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Agentic/conversational AI for banking</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Terms undisclosed. Kasisto raised ~$92M to date (clients incl. JPMorgan, Standard Chartered, TD). No revenue disclosed.</t>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Banking &amp; Lending Tech</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>26-Jun-26</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Take-Private</t>
+          <t>Capital Markets Tech</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-26</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ramsdens Holdings</t>
+          <t>Strategic M&amp;A</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>FirstCash Holdings</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>270</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>6.8</v>
+          <t>22-Jun-26</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Entendre</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>MoonPay</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Consumer financial-services and currency-exchange specialist (foreign exchange, international money transfer, secured lending) built on a traditional pawnbroking, precious-metals and jewellery-retail business across 174 UK stores</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>AI accounting agents automating bookkeeping and reporting for stablecoin and digital-asset businesses</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>BORDERLINE FINTECH (high-street pawn/FX). 600p cash/sh (~609p incl. dividend); equity ~£206M (~$273M), EV ~£203M (~$270M). LTM (Mar-26) rev ~$200M, adj. EBITDA ~$40M -&gt; EV/EBITDA ~6.8x, EV/Rev ~1.35x. [computed]</t>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Capital Markets Tech</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>26-Jun-26</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>Financial Info &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>22-Jun-26</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Entendre</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>MoonPay</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>24-Jun-26</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>First Street</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>MSCI</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>AI accounting agents automating bookkeeping and reporting for stablecoin and digital-asset businesses</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>AI-powered climate-financial intelligence platform that converts physical climate risk into property- and portfolio-level financial risk metrics</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Terms undisclosed. Early-stage (last raised $4M seed 2023, in which MoonPay participated).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Financial Info &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Strategic M&amp;A</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24-Jun-26</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>First Street</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>MSCI</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Physics-based physical climate-risk data and analytics whose AI-enabled, multi-hazard models translate climate hazards into financial risk across 2B+ structures</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>$120M cash at closing + contingent earnouts (revenue-threshold-based, first 2 yrs). Target revenue/EBITDA not disclosed; reports in MSCI's Sustainability &amp; Climate segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>InsurTech</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Asset/Book Acquisition</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24-Jun-26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Policygenius (P&amp;C book)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Matic</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>~30,000-policy property &amp; casualty insurance portfolio acquired by embedded insurtech Matic</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Book purchase price undisclosed; Matic also took an undisclosed minority growth investment from Primus Capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>InsurTech</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>PE Strategic Investment</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>22-Jun-26</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Novel Financial Holdings</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Flexpoint Ford</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Technology-enabled underwriting and insurance-services platform managing reciprocal exchanges and traditional stock insurers (~$2B gross written premium)</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Minority/strategic PE investment, terms undisclosed (Flexpoint Asset Opportunity Fund III &amp; Insurance Opportunity Fund I). ~$2B annual gross written premium. Borderline (insurance holdco, not pure tech).</t>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:R5"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -918,643 +943,882 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="54" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Target Country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lead Investor(s)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Amount ($M)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Valuation ($M)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EV / Revenue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Target Description</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Link / Press Release</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Financials &amp; basis (notes)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Asset &amp; Wealth Tech</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>22-Jun-26</t>
-        </is>
-      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fomo</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Index Ventures</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>25-Jun-26</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arca</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>General Catalyst</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Social-first consumer app simplifying on-chain crypto trading</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>AI-native wealth management firm delivering personalized, advisor-led financial services</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>$75M Series B at $550M post-money. &gt;$4B trading volume is a flow metric (not revenue); revenue not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Asset &amp; Wealth Tech</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>26-Jun-26</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>Banking &amp; Lending Tech</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>24-Jun-26</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Arca</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>General Catalyst</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Taktile</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Growth Equity</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>AI-native wealth management firm delivering personalized, advisor-led financial services</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Agentic decisioning platform automating credit, fraud, and underwriting decisions for banks and insurers</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>$48.5M Series A ($64M total incl. prior seed). Valuation not disclosed; &gt;$1B client assets (AUM, not revenue).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Banking &amp; Lending Tech</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>26-Jun-26</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24-Jun-26</t>
+          <t>Capital Markets Tech</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Taktile</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Growth Equity at Goldman Sachs Alternatives</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>22-Jun-26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Fomo</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Index Ventures</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>550</v>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Agentic decisioning platform automating credit, fraud, and underwriting decisions for banks and insurers</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Social-first consumer app simplifying on-chain crypto trading</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>$110M Series C; total funding now $184M. Valuation and revenue not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Corporate Financial Function</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>24-Jun-26</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Float Financial</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Inovia Capital</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>22-Jun-26</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Andera</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Lightspeed Venture Partners</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Canadian business finance platform -- corporate cards, expense management, bill pay, and high-yield accounts</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>AI-native platform automating the internal audit and SOX/compliance-testing function</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>C$85M (~$62M) Series C at ~C$548M (~$400M) valuation (+70%). Revenue not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Corporate Financial Function</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>26-Jun-26</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Warp</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Battery Ventures</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
+          <t>24-Jun-26</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Float Financial</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Inovia Capital</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="n">
+        <v>385</v>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>AI-native payroll-payments, tax, and benefits-finance platform within a broader HR / human-capital-management suite for high-growth companies</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Business finance platform offering corporate cards, expense management, bill pay, and high-yield accounts</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>$60M Series B (total $85M). Borderline scope (HR/payroll). Valuation/revenue not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Corporate Financial Function</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>22-Jun-26</t>
-        </is>
-      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Andera</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Lightspeed Venture Partners</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Warp</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Battery Ventures</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>AI-native platform automating the internal audit and SOX/compliance-testing function</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>AI-native HR and payroll platform automating tax, compliance, and benefits for high-growth companies</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>$37M Series A. DATE BORDERLINE: fintech.global Jun 22 vs Axios 'exclusive' Jun 17. Valuation/revenue not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Financial Info &amp; Analytics</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>23-Jun-26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Allium</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Amplify Partners</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Blockchain data platform standardizing and enriching on-chain data across 150+ chains for institutions</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Blockchain data platform standardizing and enriching on-chain data</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>$40M Series B. Valuation not disclosed; revenue +10x since Series A (no absolute figure).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>InsurTech</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>25-Jun-26</t>
-        </is>
-      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Prosus</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>520</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>5940</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>22-Jun-26</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Novel Financial Holdings</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Flexpoint Ford</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Europe's leading digital health insurer pairing insurance with a prevention and care platform</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Underwriting and insurance-services platform managing reciprocal exchanges and traditional stock insurers</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>EUR480M (~$520M) Series G at EUR5.5B (~$5.94B). ARR &gt;EUR800M (+53% YoY) -&gt; ~6.9x valuation/ARR. [computed, val/ARR]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Payments</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>26-Jun-26</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22-Jun-26</t>
+          <t>InsurTech</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CRED</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>24-Jun-26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Matic</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Primus Capital</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Indian consumer fintech for credit-card bill payments, rewards, and lending to high-credit-score members</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Embedded insurtech platform that enables lenders, banks, and financial institutions to offer personalized home and auto insurance digitally</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>$900M Series H (primary + secondary) at $4.5B post (~$4.03B pre); Meta takes ~20%. Revenue not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Payments</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>26-Jun-26</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26-Jun-26</t>
+          <t>InsurTech</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Addition</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>320</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Global cross-border payments and business-banking infrastructure for companies</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Prosus</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>6300</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Digital health insurer pairing insurance with a prevention and care platform</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>$320M Series H at $11B (up from $8B Dec-25). Revenue ~$1.3B annualized (+74% YoY) -&gt; ~8.5x valuation/revenue. ($287B TPV is flow.) [computed, val/rev]</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22-Jun-26</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CRED</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Consumer fintech for credit-card bill payments, rewards, and lending to high-credit-score members</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Global cross-border payments and business-banking infrastructure for companies</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-26</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Real Estate &amp; Mortgage Tech</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>23-Jun-26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Square Yards</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>EAAA Alternatives</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Indian real-estate transaction and mortgage / loan-distribution platform</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J14" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Real-estate transaction and mortgage / loan-distribution platform</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>Link</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>~$95M (Rs 900 Cr, debt + equity); entered unicorn club at ~$1B+ valuation. Revenue not disclosed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
